--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484857_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484857_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7379</v>
+        <v>4.8382</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.9942</v>
+        <v>0.0003</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7321</v>
+        <v>4.8379</v>
       </c>
       <c r="G2" t="n">
         <v>0.9296</v>
@@ -610,13 +610,13 @@
         <v>2.4531</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0029</v>
+        <v>0.0974</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4574</v>
+        <v>-0.4629</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4545</v>
+        <v>0.5603</v>
       </c>
       <c r="V2" t="n">
         <v>4.3772</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5745</v>
+        <v>2.7005</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6249</v>
+        <v>0.6451</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9496</v>
+        <v>2.0554</v>
       </c>
       <c r="G3" t="n">
         <v>-1.3567</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1199</v>
+        <v>0.2459</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0436</v>
+        <v>-0.0234</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1634</v>
+        <v>0.2693</v>
       </c>
       <c r="V3" t="n">
         <v>2.4904</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>O. TALENS ALBERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3932</v>
+        <v>1.1125</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.3049</v>
+        <v>0.9689</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6981</v>
+        <v>0.1436</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3644</v>
+        <v>-0.5427</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.5943</v>
+        <v>0.306</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2299</v>
+        <v>-0.8487</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.0879</v>
+        <v>-0.4868</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.1702</v>
+        <v>0.7301</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0823</v>
+        <v>-1.2169</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7235</v>
+        <v>-0.056</v>
       </c>
       <c r="N4" t="n">
         <v>-0.4241</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1476</v>
+        <v>0.3682</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1322</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0757</v>
+        <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2856</v>
+        <v>0.4857</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7265</v>
+        <v>0.2487</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5591</v>
+        <v>0.237</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3398</v>
+        <v>2.4904</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.0374</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3398</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. TALENS ALBERO</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5590000000000001</v>
+        <v>-2.6544</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4081</v>
+        <v>3.3807</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5427</v>
+        <v>-1.3644</v>
       </c>
       <c r="H5" t="n">
-        <v>0.306</v>
+        <v>-2.5943</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8487</v>
+        <v>1.2299</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4868</v>
+        <v>-2.0879</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7301</v>
+        <v>-2.1702</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2169</v>
+        <v>0.0823</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.056</v>
+        <v>0.7235</v>
       </c>
       <c r="N5" t="n">
         <v>-0.4241</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3682</v>
+        <v>1.1476</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3209</v>
+        <v>1.1322</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5096</v>
+        <v>2.0757</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3404</v>
+        <v>0.6187</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1611</v>
+        <v>0.377</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.2417</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4904</v>
+        <v>0.3398</v>
       </c>
       <c r="W5" t="n">
-        <v>4.0374</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.547</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. FELIZ CAMEAU</t>
+          <t>L. FUENTES GOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4593</v>
+        <v>-0.274</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1061</v>
+        <v>-1.3452</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3533</v>
+        <v>1.0712</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0921</v>
+        <v>-1.3109</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2827</v>
+        <v>-0.7482</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1906</v>
+        <v>-0.5628</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4194</v>
+        <v>-0.4539</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5017</v>
+        <v>0.1956</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0823</v>
+        <v>-0.6496</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6727</v>
+        <v>-0.857</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.781</v>
+        <v>-0.9438</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1083</v>
+        <v>0.0868</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9435</v>
+        <v>1.6983</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2872</v>
+        <v>-0.4727</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6011</v>
+        <v>-0.7026</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6861</v>
+        <v>0.2299</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.627</v>
+        <v>-0.6946</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7851</v>
+        <v>-1.6675</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1581</v>
+        <v>0.9729</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8558</v>
@@ -1000,13 +1000,13 @@
         <v>2.0757</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1111</v>
+        <v>-0.1787</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-0.8789</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8854</v>
+        <v>0.7002</v>
       </c>
       <c r="V7" t="n">
         <v>-1.547</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. FUENTES GOMEZ</t>
+          <t>M. PEREZ MARCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6297</v>
+        <v>-1.2076</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4627</v>
+        <v>-1.3726</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8331</v>
+        <v>0.165</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3109</v>
+        <v>-1.3351</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7482</v>
+        <v>-0.9454</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5628</v>
+        <v>-0.3897</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4539</v>
+        <v>-0.961</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1956</v>
+        <v>-0.3115</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6496</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.857</v>
+        <v>-0.3741</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9438</v>
+        <v>-0.6339</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0868</v>
+        <v>0.2598</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6983</v>
+        <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8283</v>
+        <v>-0.4385</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.4115</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.027</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. PEREZ MARCO</t>
+          <t>N. FELIZ CAMEAU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2928</v>
+        <v>-1.5326</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4313</v>
+        <v>-1.6478</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1385</v>
+        <v>0.1152</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3351</v>
+        <v>-1.0921</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9454</v>
+        <v>-1.2827</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3897</v>
+        <v>0.1906</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.961</v>
+        <v>-0.4194</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3115</v>
+        <v>-0.5017</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6496</v>
+        <v>0.0823</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3741</v>
+        <v>-0.6727</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6339</v>
+        <v>-0.781</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2598</v>
+        <v>0.1083</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5661</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5238</v>
+        <v>1.2953</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4703</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0535</v>
+        <v>0.448</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.567</v>
+        <v>-3.6771</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.2352</v>
+        <v>-4.6892</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6682</v>
+        <v>1.0121</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7055</v>
@@ -1234,13 +1234,13 @@
         <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3144</v>
+        <v>-0.4246</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0458</v>
+        <v>-0.4999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2686</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9244</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.3848</v>
+        <v>-8.185</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.6996</v>
+        <v>-11.6849</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3148</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
         <v>-6.228</v>
@@ -1312,13 +1312,13 @@
         <v>2.8305</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9493</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.94</v>
+        <v>-0.9254</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0094</v>
+        <v>0.1758</v>
       </c>
       <c r="V11" t="n">
         <v>0.6795</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.369199999999999</v>
+        <v>-6.1934</v>
       </c>
       <c r="E12" t="n">
-        <v>-24.623</v>
+        <v>-23.4473</v>
       </c>
       <c r="F12" t="n">
-        <v>17.2539</v>
+        <v>17.254</v>
       </c>
       <c r="G12" t="n">
         <v>-15.8616</v>
@@ -1372,7 +1372,7 @@
         <v>-8.878299999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3390000000000002</v>
+        <v>-0.3389999999999997</v>
       </c>
       <c r="N12" t="n">
         <v>-4.5623</v>
@@ -1390,13 +1390,13 @@
         <v>16.983</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6966999999999999</v>
+        <v>0.4789999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6072</v>
+        <v>-2.4316</v>
       </c>
       <c r="U12" t="n">
-        <v>2.9103</v>
+        <v>2.9105</v>
       </c>
       <c r="V12" t="n">
         <v>7.302300000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.927</v>
+        <v>5.9166</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5616</v>
+        <v>1.3924</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3655</v>
+        <v>4.5242</v>
       </c>
       <c r="G13" t="n">
         <v>3.6774</v>
@@ -1468,13 +1468,13 @@
         <v>2.2644</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0422</v>
+        <v>1.0317</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4225</v>
+        <v>0.2533</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6197</v>
+        <v>0.7784</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6795</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8207</v>
+        <v>5.5505</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1833</v>
+        <v>1.0858</v>
       </c>
       <c r="F14" t="n">
-        <v>5.6374</v>
+        <v>4.4646</v>
       </c>
       <c r="G14" t="n">
         <v>4.7004</v>
@@ -1546,13 +1546,13 @@
         <v>2.0757</v>
       </c>
       <c r="S14" t="n">
-        <v>2.422</v>
+        <v>1.1518</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2787</v>
+        <v>-0.3761</v>
       </c>
       <c r="U14" t="n">
-        <v>2.7007</v>
+        <v>1.5279</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2452</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.841</v>
+        <v>2.0503</v>
       </c>
       <c r="E15" t="n">
         <v>0.1679</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6731</v>
+        <v>1.8824</v>
       </c>
       <c r="G15" t="n">
         <v>0.7023</v>
@@ -1624,13 +1624,13 @@
         <v>0.9435</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3839</v>
+        <v>0.5931</v>
       </c>
       <c r="T15" t="n">
         <v>0.238</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1458</v>
+        <v>0.3551</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4217</v>
+        <v>1.6624</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.6182</v>
+        <v>-3.0336</v>
       </c>
       <c r="F16" t="n">
-        <v>5.0399</v>
+        <v>4.696</v>
       </c>
       <c r="G16" t="n">
         <v>1.3573</v>
@@ -1702,13 +1702,13 @@
         <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4609</v>
+        <v>0.7016</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6931</v>
+        <v>-0.1085</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1541</v>
+        <v>0.8102</v>
       </c>
       <c r="V16" t="n">
         <v>0.9244</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4884</v>
+        <v>0.63</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2743</v>
+        <v>-0.1768</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7627</v>
+        <v>0.8068</v>
       </c>
       <c r="G18" t="n">
         <v>1.5865</v>
@@ -1858,13 +1858,13 @@
         <v>0.3774</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3433</v>
+        <v>-0.2018</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4703</v>
+        <v>-0.3729</v>
       </c>
       <c r="U18" t="n">
-        <v>0.127</v>
+        <v>0.1711</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4526</v>
+        <v>-0.1003</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8354</v>
+        <v>-3.9328</v>
       </c>
       <c r="F19" t="n">
-        <v>3.3828</v>
+        <v>3.8325</v>
       </c>
       <c r="G19" t="n">
         <v>1.555</v>
@@ -1936,13 +1936,13 @@
         <v>2.0757</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7242</v>
+        <v>-0.372</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3963</v>
+        <v>-0.4937</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.328</v>
+        <v>0.1218</v>
       </c>
       <c r="V19" t="n">
         <v>0.6036</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6492</v>
+        <v>-0.9234</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9091</v>
+        <v>-3.104</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2599</v>
+        <v>2.1806</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4081</v>
@@ -2014,13 +2014,13 @@
         <v>0.7548</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2875</v>
+        <v>0.0132</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1205</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.167</v>
+        <v>0.0876</v>
       </c>
       <c r="V20" t="n">
         <v>0.6036</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3541</v>
+        <v>-1.0739</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5498</v>
+        <v>-0.4524</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8043</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.6397</v>
@@ -2092,13 +2092,13 @@
         <v>0.3774</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4844</v>
+        <v>-0.2041</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2939</v>
+        <v>-0.1965</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1904</v>
+        <v>-0.0076</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9434</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3192</v>
+        <v>-2.1461</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8088</v>
+        <v>-4.0036</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4895</v>
+        <v>1.8575</v>
       </c>
       <c r="G22" t="n">
         <v>-0.113</v>
@@ -2170,13 +2170,13 @@
         <v>1.887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7724</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6314</v>
+        <v>-0.8263</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.141</v>
+        <v>0.227</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1886</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.8357</v>
+        <v>-7.0599</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.582</v>
+        <v>-5.0948</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2537</v>
+        <v>-1.9651</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7462</v>
@@ -2248,13 +2248,13 @@
         <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6366000000000001</v>
+        <v>0.1392</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7055</v>
+        <v>-0.2183</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0688</v>
+        <v>0.3574</v>
       </c>
       <c r="V23" t="n">
         <v>-4.3772</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.521900000000001</v>
+        <v>5.140099999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.0309</v>
+        <v>-16.518</v>
       </c>
       <c r="F24" t="n">
-        <v>21.5528</v>
+        <v>21.658</v>
       </c>
       <c r="G24" t="n">
         <v>13.5852</v>
@@ -2326,13 +2326,13 @@
         <v>13.3977</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6356</v>
+        <v>2.2534</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6882</v>
+        <v>-2.1754</v>
       </c>
       <c r="U24" t="n">
-        <v>4.3237</v>
+        <v>4.428900000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-7.302300000000001</v>
